--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318257</v>
       </c>
       <c r="B2" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318257</v>
       </c>
       <c r="B2" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318257</v>
       </c>
       <c r="B2" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318257</v>
       </c>
       <c r="B2" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318257</v>
       </c>
       <c r="B2" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132318257</v>
+        <v>6995577</v>
       </c>
       <c r="B2" t="n">
-        <v>97990</v>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartå, Nrk</t>
+          <t>Stora Gåssjömossen (ca 3 km sv om Svartå), Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470257</v>
+        <v>470261</v>
       </c>
       <c r="R2" t="n">
-        <v>6552249</v>
+        <v>6552545</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2012-08-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2012-08-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,18 +766,130 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad barrskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132318257</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svartå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>470257</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6552249</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,48 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132318257</v>
+        <v>134759932</v>
       </c>
       <c r="B3" t="n">
-        <v>98060</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartå, Nrk</t>
+          <t>Björnlund, Björnlund, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470257</v>
+        <v>470175</v>
       </c>
       <c r="R3" t="n">
-        <v>6552249</v>
+        <v>6552562</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,17 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,15 +886,1169 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134764775</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>470102</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6552604</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134764818</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>470102</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6552604</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>19 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134760874</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57796</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>470150</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Noterad 3 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134760628</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>470150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Noterad 13 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134760018</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>470061</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6552534</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134760768</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>470150</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterad 160 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134764845</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>470102</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6552604</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>112 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134760853</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>470150</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>04:29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Noterad 229 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132318257</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>470257</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6552249</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134759909</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>470156</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1127,43 +1127,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134760874</v>
+        <v>135429632</v>
       </c>
       <c r="B6" t="n">
-        <v>57796</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102976</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470150</v>
+        <v>470087</v>
       </c>
       <c r="R6" t="n">
-        <v>6552494</v>
+        <v>6552631</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,27 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:57</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Noterad 3 ggr under perioden.</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,38 +1229,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134760628</v>
+        <v>135429676</v>
       </c>
       <c r="B7" t="n">
-        <v>58519</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470150</v>
+        <v>470136</v>
       </c>
       <c r="R7" t="n">
-        <v>6552494</v>
+        <v>6552601</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1319,27 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>04:56</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>04:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Noterad 13 ggr under perioden.</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,42 +1335,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134760018</v>
+        <v>134760874</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>57796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>102976</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1410,13 +1380,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470061</v>
+        <v>470150</v>
       </c>
       <c r="R8" t="n">
-        <v>6552534</v>
+        <v>6552494</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,22 +1410,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Noterad 3 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134760768</v>
+        <v>134760628</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>58519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,29 +1468,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1562,22 +1532,22 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>04:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>04:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Noterad 160 ggr under perioden.</t>
+          <t>Noterad 13 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134764845</v>
+        <v>134760018</v>
       </c>
       <c r="B10" t="n">
         <v>58136</v>
@@ -1632,10 +1602,14 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470102</v>
+        <v>470061</v>
       </c>
       <c r="R10" t="n">
-        <v>6552604</v>
+        <v>6552534</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1674,27 +1648,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>112 noteringar under perioden</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,32 +1690,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134760853</v>
+        <v>134760768</v>
       </c>
       <c r="B11" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1801,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>04:29</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,12 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Noterad 229 ggr under perioden.</t>
+          <t>Noterad 160 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,48 +1812,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132318257</v>
+        <v>134764845</v>
       </c>
       <c r="B12" t="n">
-        <v>98060</v>
+        <v>58136</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartå, Nrk</t>
+          <t>Björnlund, Björnlund, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470257</v>
+        <v>470102</v>
       </c>
       <c r="R12" t="n">
-        <v>6552249</v>
+        <v>6552604</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,17 +1882,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>112 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,57 +1917,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134759909</v>
+        <v>135429737</v>
       </c>
       <c r="B13" t="n">
-        <v>98060</v>
+        <v>58136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnlund, Björnlund, Nrk</t>
+          <t>Sirsjöängen, Sirsjöängen, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470156</v>
+        <v>470206</v>
       </c>
       <c r="R13" t="n">
-        <v>6552494</v>
+        <v>6552430</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2010,22 +2003,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,6 +2032,337 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134760853</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>470150</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>04:29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Noterad 229 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132318257</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>470257</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6552249</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134759909</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>470156</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135429632</v>
+        <v>135441538</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,27 +1138,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470087</v>
+        <v>470156</v>
       </c>
       <c r="R6" t="n">
-        <v>6552631</v>
+        <v>6552574</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1202,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Noterad 8 ggr under 4 dagar under perioden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135429676</v>
+        <v>135429632</v>
       </c>
       <c r="B7" t="n">
         <v>57162</v>
@@ -1257,14 +1267,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1273,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470136</v>
+        <v>470087</v>
       </c>
       <c r="R7" t="n">
-        <v>6552601</v>
+        <v>6552631</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1335,43 +1341,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134760874</v>
+        <v>135429676</v>
       </c>
       <c r="B8" t="n">
-        <v>57796</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102976</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1380,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470150</v>
+        <v>470136</v>
       </c>
       <c r="R8" t="n">
-        <v>6552494</v>
+        <v>6552601</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,27 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>19:57</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Noterad 3 ggr under perioden.</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,27 +1447,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134760628</v>
+        <v>134760874</v>
       </c>
       <c r="B9" t="n">
-        <v>58519</v>
+        <v>57796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1486,6 +1476,11 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1503,7 +1498,7 @@
         <v>6552494</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,27 +1522,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>04:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>04:20</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Noterad 13 ggr under perioden.</t>
+          <t>Noterad 3 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134760018</v>
+        <v>134760628</v>
       </c>
       <c r="B10" t="n">
-        <v>58136</v>
+        <v>58519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,31 +1580,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1618,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470061</v>
+        <v>470150</v>
       </c>
       <c r="R10" t="n">
-        <v>6552534</v>
+        <v>6552494</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1648,22 +1639,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>04:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Noterad 13 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134760768</v>
+        <v>134760018</v>
       </c>
       <c r="B11" t="n">
         <v>58136</v>
@@ -1718,15 +1714,14 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1735,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470150</v>
+        <v>470061</v>
       </c>
       <c r="R11" t="n">
-        <v>6552494</v>
+        <v>6552534</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1765,12 +1760,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Noterad 160 ggr under perioden.</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134764845</v>
+        <v>134760768</v>
       </c>
       <c r="B12" t="n">
         <v>58136</v>
@@ -1841,6 +1831,11 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470102</v>
+        <v>470150</v>
       </c>
       <c r="R12" t="n">
-        <v>6552604</v>
+        <v>6552494</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1882,27 +1877,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>112 noteringar under perioden</t>
+          <t>Noterad 160 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,7 +1924,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135429737</v>
+        <v>134764845</v>
       </c>
       <c r="B13" t="n">
         <v>58136</v>
@@ -1957,26 +1952,22 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="I13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sirsjöängen, Sirsjöängen, Nrk</t>
+          <t>Björnlund, Björnlund, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470206</v>
+        <v>470102</v>
       </c>
       <c r="R13" t="n">
-        <v>6552430</v>
+        <v>6552604</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2003,12 +1994,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>112 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,55 +2041,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134760853</v>
+        <v>135429737</v>
       </c>
       <c r="B14" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnlund, Björnlund, Nrk</t>
+          <t>Sirsjöängen, Sirsjöängen, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470150</v>
+        <v>470206</v>
       </c>
       <c r="R14" t="n">
-        <v>6552494</v>
+        <v>6552430</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2110,27 +2115,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>04:29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Noterad 229 ggr under perioden.</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,48 +2147,58 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132318257</v>
+        <v>135441598</v>
       </c>
       <c r="B15" t="n">
-        <v>98060</v>
+        <v>58136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartå, Nrk</t>
+          <t>Björnlund, Björnlund, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470257</v>
+        <v>470156</v>
       </c>
       <c r="R15" t="n">
-        <v>6552249</v>
+        <v>6552574</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2222,17 +2222,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Noterad 46 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,22 +2247,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134759909</v>
+        <v>134760853</v>
       </c>
       <c r="B16" t="n">
-        <v>98060</v>
+        <v>58131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,31 +2270,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>103023</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnlund, Björnlund, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470156</v>
+        <v>470150</v>
       </c>
       <c r="R16" t="n">
         <v>6552494</v>
@@ -2324,22 +2334,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>04:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Noterad 229 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,6 +2378,327 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135441551</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>470156</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6552574</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Noterad 136 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132318257</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svartå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>470257</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6552249</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134759909</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>470156</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132318257</v>
+        <v>135485297</v>
       </c>
       <c r="B18" t="n">
-        <v>98060</v>
+        <v>56842</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,37 +2504,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>205992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartå, Nrk</t>
+          <t>Björnlund, Björnlund, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470257</v>
+        <v>470123</v>
       </c>
       <c r="R18" t="n">
-        <v>6552249</v>
+        <v>6552572</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2558,17 +2568,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>23:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>23:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,22 +2598,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134759909</v>
+        <v>135485325</v>
       </c>
       <c r="B19" t="n">
-        <v>98060</v>
+        <v>56854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,34 +2621,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>205995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Björnlund, Björnlund, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470156</v>
+        <v>470123</v>
       </c>
       <c r="R19" t="n">
-        <v>6552494</v>
+        <v>6552572</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2660,22 +2685,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>01:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>01:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,6 +2724,328 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135485312</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>470123</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6552572</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132318257</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svartå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>470257</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6552249</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134759909</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>470156</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6995577</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759932</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134764775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134764818</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135441538</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429632</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429676</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760874</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1683,6 +1728,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760628</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,6 +1849,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1921,6 +1976,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760768</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2038,6 +2098,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134764845</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2144,6 +2209,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429737</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2256,6 +2326,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135441598</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2378,6 +2453,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760853</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2490,6 +2570,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135441551</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2607,6 +2692,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485297</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2724,6 +2814,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485325</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2837,6 +2932,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485312</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2939,6 +3039,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318257</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3046,8 +3151,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759909</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -1155,7 +1155,7 @@
         <v>135441538</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135429632</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135429676</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135429737</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>135441598</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>135441551</v>
       </c>
       <c r="B17" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>135485297</v>
       </c>
       <c r="B18" t="n">
-        <v>56842</v>
+        <v>56847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>135485325</v>
       </c>
       <c r="B19" t="n">
-        <v>56854</v>
+        <v>56859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>135485312</v>
       </c>
       <c r="B20" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 15809-2026 artfynd.xlsx
+++ b/artfynd/A 15809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1152,27 +1152,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134760874</v>
+        <v>135441538</v>
       </c>
       <c r="B6" t="n">
-        <v>57796</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102976</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470150</v>
+        <v>470156</v>
       </c>
       <c r="R6" t="n">
-        <v>6552494</v>
+        <v>6552574</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1227,27 +1227,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:57</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Noterad 3 ggr under perioden.</t>
+          <t>Noterad 8 ggr under 4 dagar under perioden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,44 +1263,44 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760874</t>
+          <t>https://artportalen.se/Sighting/135441538</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134760628</v>
+        <v>135429632</v>
       </c>
       <c r="B7" t="n">
-        <v>58519</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470150</v>
+        <v>470087</v>
       </c>
       <c r="R7" t="n">
-        <v>6552494</v>
+        <v>6552631</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1349,27 +1339,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>04:56</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>04:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Noterad 13 ggr under perioden.</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,48 +1370,48 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760628</t>
+          <t>https://artportalen.se/Sighting/135429632</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134760018</v>
+        <v>135429676</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>57167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1445,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470061</v>
+        <v>470136</v>
       </c>
       <c r="R8" t="n">
-        <v>6552534</v>
+        <v>6552601</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1475,22 +1450,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,44 +1481,44 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760018</t>
+          <t>https://artportalen.se/Sighting/135429676</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134760768</v>
+        <v>134760874</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>57796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1573,7 +1538,7 @@
         <v>6552494</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,27 +1562,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Noterad 160 ggr under perioden.</t>
+          <t>Noterad 3 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,16 +1608,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760768</t>
+          <t>https://artportalen.se/Sighting/134760874</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134764845</v>
+        <v>134760628</v>
       </c>
       <c r="B10" t="n">
-        <v>58136</v>
+        <v>58519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,21 +1625,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1689,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470102</v>
+        <v>470150</v>
       </c>
       <c r="R10" t="n">
-        <v>6552604</v>
+        <v>6552494</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1719,27 +1684,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>04:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>04:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>112 noteringar under perioden</t>
+          <t>Noterad 13 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,49 +1730,48 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134764845</t>
+          <t>https://artportalen.se/Sighting/134760628</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134760853</v>
+        <v>134760018</v>
       </c>
       <c r="B11" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1816,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470150</v>
+        <v>470061</v>
       </c>
       <c r="R11" t="n">
-        <v>6552494</v>
+        <v>6552534</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1846,12 +1810,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>04:29</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1861,12 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Noterad 229 ggr under perioden.</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,54 +1851,64 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760853</t>
+          <t>https://artportalen.se/Sighting/134760018</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132318257</v>
+        <v>134760768</v>
       </c>
       <c r="B12" t="n">
-        <v>98060</v>
+        <v>58136</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartå, Nrk</t>
+          <t>Björnlund, Björnlund, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470257</v>
+        <v>470150</v>
       </c>
       <c r="R12" t="n">
-        <v>6552249</v>
+        <v>6552494</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,17 +1932,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Noterad 160 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,62 +1967,67 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132318257</t>
+          <t>https://artportalen.se/Sighting/134760768</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134759909</v>
+        <v>134764845</v>
       </c>
       <c r="B13" t="n">
-        <v>98060</v>
+        <v>58136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnlund, Björnlund, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470156</v>
+        <v>470102</v>
       </c>
       <c r="R13" t="n">
-        <v>6552494</v>
+        <v>6552604</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2070,22 +2054,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>112 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,6 +2099,1059 @@
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134764845</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135429737</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sirsjöängen, Sirsjöängen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>470206</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6552430</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429737</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135441598</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>470156</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6552574</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Noterad 46 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135441598</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134760853</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>470150</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>04:29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Noterad 229 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760853</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135441551</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>470156</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6552574</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Noterad 136 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135441551</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135485297</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56847</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>470123</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6552572</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485297</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135485325</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56859</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>470123</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6552572</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485325</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135485312</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56838</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>470123</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6552572</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485312</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132318257</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svartå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>470257</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6552249</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318257</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134759909</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Björnlund, Björnlund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>470156</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6552494</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134759909</t>
         </is>
@@ -2129,6 +3171,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
